--- a/elite-data/manifest-templates/EL_template_AssayRNAseqTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayRNAseqTemplate.xlsx
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="82">
   <si>
     <t>Filename</t>
   </si>
@@ -325,43 +325,49 @@
     <t>MetaboLights</t>
   </si>
   <si>
-    <t>sac-seq</t>
+    <t>Qiagen Rneasy Extraction Kit</t>
   </si>
   <si>
     <t>Metabolomics Workbench</t>
   </si>
   <si>
-    <t>Smart-seq1</t>
+    <t>sac-seq</t>
   </si>
   <si>
     <t>MGnify</t>
   </si>
   <si>
-    <t>Smart-seq2</t>
+    <t>Smart-seq1</t>
   </si>
   <si>
     <t>NCBI Gene</t>
   </si>
   <si>
+    <t>Smart-seq2</t>
+  </si>
+  <si>
     <t>Smart-seq4</t>
+  </si>
+  <si>
+    <t>SMRTbell</t>
+  </si>
+  <si>
+    <t>TruSeq</t>
+  </si>
+  <si>
+    <t>Ultralow Methyl-Seq</t>
   </si>
   <si>
     <t>PRIDE</t>
   </si>
   <si>
-    <t>SMRTbell</t>
-  </si>
-  <si>
     <t>SRA</t>
   </si>
   <si>
-    <t>TruSeq</t>
+    <t>Synapse</t>
   </si>
   <si>
     <t>UniProt</t>
-  </si>
-  <si>
-    <t>Ultralow Methyl-Seq</t>
   </si>
 </sst>
 </file>
@@ -27735,20 +27741,20 @@
     </row>
   </sheetData>
   <dataValidations>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="L2:L1000">
+      <formula1>Sheet2!$L$2:$L$23</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="N2:N1000">
       <formula1>Sheet2!$N$2:$N$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
+      <formula1>Sheet2!$H$2:$H$27</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="I2:I1000">
       <formula1>Sheet2!$I$2:$I$10</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="O2:O1000">
       <formula1>Sheet2!$O$2:$O$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
-      <formula1>Sheet2!$H$2:$H$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="L2:L1000">
-      <formula1>Sheet2!$L$2:$L$22</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="R2:R1000">
       <formula1>Sheet2!$R$2:$R$8</formula1>
@@ -28071,30 +28077,61 @@
     </row>
     <row r="19">
       <c r="H19" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="L19" s="7" t="s">
+    </row>
+    <row r="20">
+      <c r="H20" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="20">
-      <c r="H20" s="7" t="s">
+    <row r="21">
+      <c r="H21" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="L21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L20" s="7" t="s">
+    </row>
+    <row r="22">
+      <c r="H22" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L22" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="21">
-      <c r="H21" s="7" t="s">
+    <row r="23">
+      <c r="H23" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="L21" s="7" t="s">
+      <c r="L23" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22">
-      <c r="L22" s="7" t="s">
+    <row r="25">
+      <c r="H25" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" s="7" t="s">
         <v>54</v>
       </c>
     </row>

--- a/elite-data/manifest-templates/EL_template_AssayRNAseqTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayRNAseqTemplate.xlsx
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="83">
   <si>
     <t>Filename</t>
   </si>
@@ -289,7 +289,7 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>GENCODEv38 GRCh38</t>
+    <t>GENCODEv38</t>
   </si>
   <si>
     <t>total RNA minus rRNA</t>
@@ -307,43 +307,46 @@
     <t>GISAID</t>
   </si>
   <si>
+    <t>GRCh38</t>
+  </si>
+  <si>
     <t>IEDB</t>
+  </si>
+  <si>
+    <t>Omni-ATAC</t>
   </si>
   <si>
     <t>ImmPort</t>
   </si>
   <si>
-    <t>Omni-ATAC</t>
+    <t>Qiagen PreAnalytiX PAXgene Blood miRNA Kit</t>
   </si>
   <si>
     <t>MassIVE</t>
   </si>
   <si>
-    <t>Qiagen PreAnalytiX PAXgene Blood miRNA Kit</t>
+    <t>Qiagen Rneasy Extraction Kit</t>
   </si>
   <si>
     <t>MetaboLights</t>
   </si>
   <si>
-    <t>Qiagen Rneasy Extraction Kit</t>
+    <t>sac-seq</t>
   </si>
   <si>
     <t>Metabolomics Workbench</t>
   </si>
   <si>
-    <t>sac-seq</t>
+    <t>Smart-seq1</t>
   </si>
   <si>
     <t>MGnify</t>
   </si>
   <si>
-    <t>Smart-seq1</t>
+    <t>Smart-seq2</t>
   </si>
   <si>
     <t>NCBI Gene</t>
-  </si>
-  <si>
-    <t>Smart-seq2</t>
   </si>
   <si>
     <t>Smart-seq4</t>
@@ -27751,9 +27754,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="N2:N1000">
       <formula1>Sheet2!$N$2:$N$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
-      <formula1>Sheet2!$H$2:$H$27</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="I2:I1000">
       <formula1>Sheet2!$I$2:$I$10</formula1>
     </dataValidation>
@@ -27762,6 +27762,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="R2:R1000">
       <formula1>Sheet2!$R$2:$R$8</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
+      <formula1>Sheet2!$H$2:$H$28</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="J2:J1000">
       <formula1>Sheet2!$J$2:$J$9</formula1>
@@ -28081,39 +28084,39 @@
     </row>
     <row r="19">
       <c r="H19" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L19" s="7" t="s">
-        <v>74</v>
+      <c r="L20" s="7" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="20">
-      <c r="H20" s="7" t="s">
+    <row r="21">
+      <c r="H21" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L20" s="7" t="s">
-        <v>75</v>
+      <c r="L21" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="21">
-      <c r="H21" s="7" t="s">
+    <row r="22">
+      <c r="H22" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="L21" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="H22" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="L22" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23">
       <c r="H23" s="7" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>54</v>
@@ -28136,6 +28139,11 @@
     </row>
     <row r="27">
       <c r="H27" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" s="7" t="s">
         <v>54</v>
       </c>
     </row>

--- a/elite-data/manifest-templates/EL_template_AssayRNAseqTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayRNAseqTemplate.xlsx
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="82">
   <si>
     <t>Filename</t>
   </si>
@@ -271,7 +271,7 @@
     <t>stranded</t>
   </si>
   <si>
-    <t>singleEnd pairedEnd</t>
+    <t>Unknown</t>
   </si>
   <si>
     <t>GenBank</t>
@@ -284,9 +284,6 @@
   </si>
   <si>
     <t>NEBNext</t>
-  </si>
-  <si>
-    <t>Unknown</t>
   </si>
   <si>
     <t>GENCODEv38</t>
@@ -27761,7 +27758,7 @@
       <formula1>Sheet2!$O$2:$O$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="R2:R1000">
-      <formula1>Sheet2!$R$2:$R$8</formula1>
+      <formula1>Sheet2!$R$2:$R$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
       <formula1>Sheet2!$H$2:$H$28</formula1>
@@ -27984,35 +27981,32 @@
         <v>53</v>
       </c>
       <c r="O8" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="R8" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="H9" s="7" t="s">
+      <c r="I9" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="J9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="L9" s="7" t="s">
+      <c r="O9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="O9" s="7" t="s">
+    </row>
+    <row r="10">
+      <c r="H10" s="7" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="H10" s="7" t="s">
-        <v>59</v>
-      </c>
       <c r="I10" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>27</v>
@@ -28020,7 +28014,7 @@
     </row>
     <row r="11">
       <c r="H11" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>32</v>
@@ -28028,7 +28022,7 @@
     </row>
     <row r="12">
       <c r="H12" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>35</v>
@@ -28036,58 +28030,58 @@
     </row>
     <row r="13">
       <c r="H13" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="L13" s="7" t="s">
+    </row>
+    <row r="14">
+      <c r="H14" s="7" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="H14" s="7" t="s">
+      <c r="L14" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="L14" s="7" t="s">
+    </row>
+    <row r="15">
+      <c r="H15" s="7" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="H15" s="7" t="s">
+      <c r="L15" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="L15" s="7" t="s">
+    </row>
+    <row r="16">
+      <c r="H16" s="7" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="H16" s="7" t="s">
+      <c r="L16" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="L16" s="7" t="s">
+    </row>
+    <row r="17">
+      <c r="H17" s="7" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="H17" s="7" t="s">
+      <c r="L17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="L17" s="7" t="s">
+    </row>
+    <row r="18">
+      <c r="H18" s="7" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="H18" s="7" t="s">
+      <c r="L18" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="L18" s="7" t="s">
+    </row>
+    <row r="19">
+      <c r="H19" s="7" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="H19" s="7" t="s">
+      <c r="L19" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="20">
@@ -28095,7 +28089,7 @@
         <v>27</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
@@ -28103,7 +28097,7 @@
         <v>32</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22">
@@ -28111,7 +28105,7 @@
         <v>35</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23">
@@ -28119,32 +28113,32 @@
         <v>45</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
       <c r="H24" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="H25" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="25">
-      <c r="H25" s="7" t="s">
+    <row r="26">
+      <c r="H26" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26">
-      <c r="H26" s="7" t="s">
+    <row r="27">
+      <c r="H27" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="27">
-      <c r="H27" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
     <row r="28">
       <c r="H28" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/elite-data/manifest-templates/EL_template_AssayRNAseqTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayRNAseqTemplate.xlsx
@@ -205,7 +205,7 @@
     <t>forward</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>Broad Single Cell Portal</t>
@@ -220,7 +220,7 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>dbGAP</t>
@@ -271,7 +271,7 @@
     <t>stranded</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>GenBank</t>
